--- a/Team-Data/2014-15/3-11-2014-15.xlsx
+++ b/Team-Data/2014-15/3-11-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,70 +728,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
         <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>0.781</v>
+        <v>0.794</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
       </c>
       <c r="I2" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J2" t="n">
         <v>81.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="N2" t="n">
-        <v>0.385</v>
+        <v>0.386</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P2" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.779</v>
+        <v>0.776</v>
       </c>
       <c r="R2" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U2" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="V2" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X2" t="n">
         <v>4.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z2" t="n">
         <v>17.8</v>
@@ -736,13 +803,13 @@
         <v>102.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -766,13 +833,13 @@
         <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN2" t="n">
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
         <v>22</v>
@@ -796,13 +863,13 @@
         <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -843,22 +910,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
         <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.429</v>
+        <v>0.419</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J3" t="n">
         <v>88.3</v>
@@ -876,10 +943,10 @@
         <v>0.331</v>
       </c>
       <c r="O3" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P3" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
         <v>0.755</v>
@@ -888,13 +955,13 @@
         <v>11.3</v>
       </c>
       <c r="S3" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T3" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="U3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="V3" t="n">
         <v>13.9</v>
@@ -909,28 +976,28 @@
         <v>5.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA3" t="n">
         <v>18.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
         <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>10</v>
@@ -966,10 +1033,10 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -981,19 +1048,19 @@
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
         <v>26</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
         <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>0.397</v>
+        <v>0.403</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J4" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="K4" t="n">
         <v>0.447</v>
@@ -1058,52 +1125,52 @@
         <v>0.327</v>
       </c>
       <c r="O4" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R4" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S4" t="n">
         <v>31.9</v>
       </c>
       <c r="T4" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W4" t="n">
         <v>6.9</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z4" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AA4" t="n">
         <v>20</v>
       </c>
-      <c r="AA4" t="n">
-        <v>20.1</v>
-      </c>
       <c r="AB4" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="AC4" t="n">
         <v>-3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1115,13 +1182,13 @@
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1133,13 +1200,13 @@
         <v>20</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
         <v>22</v>
@@ -1148,16 +1215,16 @@
         <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1169,16 +1236,16 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB4" t="n">
         <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E5" t="n">
         <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.444</v>
+        <v>0.452</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
         <v>0.427</v>
@@ -1246,7 +1313,7 @@
         <v>23</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.74</v>
+        <v>0.743</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
@@ -1258,7 +1325,7 @@
         <v>44.1</v>
       </c>
       <c r="U5" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V5" t="n">
         <v>12</v>
@@ -1267,43 +1334,43 @@
         <v>5.9</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y5" t="n">
         <v>5.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
         <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE5" t="n">
         <v>18</v>
       </c>
-      <c r="AE5" t="n">
-        <v>19</v>
-      </c>
       <c r="AF5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG5" t="n">
         <v>18</v>
       </c>
-      <c r="AG5" t="n">
-        <v>19</v>
-      </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
         <v>28</v>
@@ -1321,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
         <v>23</v>
@@ -1345,13 +1412,13 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -1389,19 +1456,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
         <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>0.606</v>
+        <v>0.6</v>
       </c>
       <c r="H6" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I6" t="n">
         <v>36.6</v>
@@ -1416,28 +1483,28 @@
         <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="P6" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S6" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="T6" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="U6" t="n">
         <v>21.6</v>
@@ -1449,28 +1516,28 @@
         <v>6.1</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y6" t="n">
         <v>5.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
@@ -1479,10 +1546,10 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AI6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ6" t="n">
         <v>17</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1515,10 +1582,10 @@
         <v>6</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV6" t="n">
         <v>15</v>
@@ -1527,16 +1594,16 @@
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -1652,19 +1719,19 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
         <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
         <v>22</v>
@@ -1682,7 +1749,7 @@
         <v>8</v>
       </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP7" t="n">
         <v>8</v>
@@ -1694,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
         <v>17</v>
@@ -1703,7 +1770,7 @@
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
@@ -1712,10 +1779,10 @@
         <v>26</v>
       </c>
       <c r="AY7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E8" t="n">
         <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.631</v>
+        <v>0.621</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,7 +1838,7 @@
         <v>39.3</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.459</v>
@@ -1780,40 +1847,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="N8" t="n">
         <v>0.349</v>
       </c>
       <c r="O8" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P8" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y8" t="n">
         <v>3.8</v>
@@ -1828,19 +1895,19 @@
         <v>104.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>15</v>
@@ -1852,10 +1919,10 @@
         <v>9</v>
       </c>
       <c r="AK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL8" t="n">
         <v>8</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>7</v>
       </c>
       <c r="AM8" t="n">
         <v>6</v>
@@ -1870,16 +1937,16 @@
         <v>21</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1900,13 +1967,13 @@
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
         <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>0.369</v>
+        <v>0.359</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1953,28 +2020,28 @@
         <v>37.2</v>
       </c>
       <c r="J9" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.43</v>
+        <v>0.429</v>
       </c>
       <c r="L9" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.316</v>
+        <v>0.314</v>
       </c>
       <c r="O9" t="n">
         <v>17.9</v>
       </c>
       <c r="P9" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R9" t="n">
         <v>12.2</v>
@@ -1986,46 +2053,46 @@
         <v>44.7</v>
       </c>
       <c r="U9" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V9" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W9" t="n">
         <v>7.5</v>
       </c>
       <c r="X9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.7</v>
+        <v>-4</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="n">
         <v>18</v>
@@ -2046,7 +2113,7 @@
         <v>29</v>
       </c>
       <c r="AO9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
         <v>7</v>
@@ -2058,25 +2125,25 @@
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
         <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
@@ -2088,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -2117,55 +2184,55 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>0.359</v>
+        <v>0.365</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J10" t="n">
-        <v>86.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>0.426</v>
       </c>
       <c r="L10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M10" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="N10" t="n">
         <v>0.335</v>
       </c>
       <c r="O10" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.708</v>
+        <v>0.707</v>
       </c>
       <c r="R10" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S10" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T10" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="U10" t="n">
         <v>21.1</v>
@@ -2174,7 +2241,7 @@
         <v>13.8</v>
       </c>
       <c r="W10" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X10" t="n">
         <v>4.5</v>
@@ -2183,37 +2250,37 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB10" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
         <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK10" t="n">
         <v>29</v>
@@ -2222,16 +2289,16 @@
         <v>10</v>
       </c>
       <c r="AM10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN10" t="n">
         <v>21</v>
       </c>
       <c r="AO10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>4</v>
@@ -2252,7 +2319,7 @@
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
         <v>18</v>
@@ -2264,7 +2331,7 @@
         <v>9</v>
       </c>
       <c r="BA10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2317,25 +2384,25 @@
         <v>41.4</v>
       </c>
       <c r="J11" t="n">
-        <v>86.7</v>
+        <v>86.8</v>
       </c>
       <c r="K11" t="n">
         <v>0.477</v>
       </c>
       <c r="L11" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="M11" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.391</v>
+        <v>0.392</v>
       </c>
       <c r="O11" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q11" t="n">
         <v>0.768</v>
@@ -2347,16 +2414,16 @@
         <v>34.5</v>
       </c>
       <c r="T11" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="V11" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W11" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X11" t="n">
         <v>6.1</v>
@@ -2365,19 +2432,19 @@
         <v>3.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB11" t="n">
         <v>109.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2410,13 +2477,13 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP11" t="n">
         <v>24</v>
       </c>
-      <c r="AP11" t="n">
-        <v>25</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2431,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW11" t="n">
         <v>4</v>
@@ -2443,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -2484,22 +2551,22 @@
         <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
@@ -2508,37 +2575,37 @@
         <v>11.6</v>
       </c>
       <c r="M12" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V12" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="W12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="X12" t="n">
         <v>4.8</v>
@@ -2547,28 +2614,28 @@
         <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
         <v>16</v>
@@ -2577,7 +2644,7 @@
         <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2595,7 +2662,7 @@
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2616,25 +2683,25 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="n">
         <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>0.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>17</v>
@@ -2786,7 +2853,7 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>5</v>
@@ -2801,7 +2868,7 @@
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
         <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>0.646</v>
+        <v>0.641</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2863,28 +2930,28 @@
         <v>39.2</v>
       </c>
       <c r="J14" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.47</v>
       </c>
       <c r="L14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="O14" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="P14" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.717</v>
+        <v>0.716</v>
       </c>
       <c r="R14" t="n">
         <v>9.5</v>
@@ -2893,7 +2960,7 @@
         <v>32.8</v>
       </c>
       <c r="T14" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U14" t="n">
         <v>24.4</v>
@@ -2911,22 +2978,22 @@
         <v>3.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.2</v>
+        <v>106</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2956,7 +3023,7 @@
         <v>4</v>
       </c>
       <c r="AO14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
@@ -2989,10 +3056,10 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N15" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O15" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="P15" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>12.9</v>
@@ -3093,19 +3160,19 @@
         <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,10 +3187,10 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
@@ -3144,16 +3211,16 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT15" t="n">
         <v>12</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>11</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3165,19 +3232,19 @@
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" t="n">
         <v>45</v>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.703</v>
+        <v>0.714</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
@@ -3227,7 +3294,7 @@
         <v>38</v>
       </c>
       <c r="J16" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.459</v>
@@ -3239,16 +3306,16 @@
         <v>15.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O16" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R16" t="n">
         <v>10.3</v>
@@ -3263,7 +3330,7 @@
         <v>21.9</v>
       </c>
       <c r="V16" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W16" t="n">
         <v>8.699999999999999</v>
@@ -3278,16 +3345,16 @@
         <v>18.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,16 +3366,16 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>11</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3320,25 +3387,25 @@
         <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP16" t="n">
         <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV16" t="n">
         <v>6</v>
@@ -3359,7 +3426,7 @@
         <v>14</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" t="n">
         <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>0.453</v>
+        <v>0.444</v>
       </c>
       <c r="H17" t="n">
         <v>48.2</v>
@@ -3409,7 +3476,7 @@
         <v>34.7</v>
       </c>
       <c r="J17" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0.456</v>
@@ -3421,19 +3488,19 @@
         <v>20.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O17" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P17" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="R17" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S17" t="n">
         <v>29.7</v>
@@ -3442,43 +3509,43 @@
         <v>38.6</v>
       </c>
       <c r="U17" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V17" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W17" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X17" t="n">
         <v>4.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA17" t="n">
         <v>21</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
         <v>25</v>
@@ -3490,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3505,16 +3572,16 @@
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3523,19 +3590,19 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW17" t="n">
         <v>10</v>
       </c>
       <c r="AX17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY17" t="n">
         <v>6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
         <v>8</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18" t="n">
         <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.531</v>
+        <v>0.524</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3603,31 +3670,31 @@
         <v>18.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O18" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
         <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R18" t="n">
         <v>10.1</v>
       </c>
       <c r="S18" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V18" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="W18" t="n">
         <v>9.6</v>
@@ -3639,7 +3706,7 @@
         <v>4.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA18" t="n">
         <v>19.8</v>
@@ -3648,10 +3715,10 @@
         <v>97.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3669,13 +3736,13 @@
         <v>16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK18" t="n">
         <v>5</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
         <v>25</v>
@@ -3690,7 +3757,7 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>24</v>
@@ -3699,7 +3766,7 @@
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3708,19 +3775,19 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ18" t="n">
         <v>25</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" t="n">
         <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,37 +3840,37 @@
         <v>36.6</v>
       </c>
       <c r="J19" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K19" t="n">
         <v>0.434</v>
       </c>
       <c r="L19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M19" t="n">
         <v>14.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.327</v>
+        <v>0.33</v>
       </c>
       <c r="O19" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P19" t="n">
         <v>25.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
       <c r="R19" t="n">
         <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T19" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="U19" t="n">
         <v>21.9</v>
@@ -3818,10 +3885,10 @@
         <v>3.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA19" t="n">
         <v>21.7</v>
@@ -3830,10 +3897,10 @@
         <v>97.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7.8</v>
+        <v>-7.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3848,10 +3915,10 @@
         <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3863,7 +3930,7 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3872,19 +3939,19 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV19" t="n">
         <v>22</v>
@@ -3902,7 +3969,7 @@
         <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
         <v>29</v>
       </c>
       <c r="G20" t="n">
-        <v>0.547</v>
+        <v>0.554</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -3967,37 +4034,37 @@
         <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O20" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P20" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
         <v>21.8</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W20" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,61 +4073,61 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
         <v>99.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI20" t="n">
         <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM20" t="n">
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>16</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR20" t="n">
         <v>8</v>
       </c>
-      <c r="AR20" t="n">
-        <v>10</v>
-      </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
         <v>16</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4221,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4251,7 +4318,7 @@
         <v>18</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
         <v>23</v>
@@ -4263,7 +4330,7 @@
         <v>7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" t="n">
         <v>35</v>
       </c>
       <c r="F22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G22" t="n">
-        <v>0.547</v>
+        <v>0.556</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
@@ -4319,73 +4386,73 @@
         <v>38.3</v>
       </c>
       <c r="J22" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="K22" t="n">
         <v>0.445</v>
       </c>
       <c r="L22" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
         <v>22.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="O22" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P22" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R22" t="n">
         <v>12.3</v>
       </c>
       <c r="S22" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="T22" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="U22" t="n">
         <v>20.7</v>
       </c>
       <c r="V22" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W22" t="n">
         <v>7.2</v>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y22" t="n">
         <v>4.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.4</v>
+        <v>102.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
         <v>13</v>
@@ -4397,7 +4464,7 @@
         <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
@@ -4409,10 +4476,10 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
@@ -4424,7 +4491,7 @@
         <v>2</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
@@ -4433,22 +4500,22 @@
         <v>23</v>
       </c>
       <c r="AV22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW22" t="n">
         <v>22</v>
       </c>
       <c r="AX22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -4507,31 +4574,31 @@
         <v>0.455</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.355</v>
+        <v>0.352</v>
       </c>
       <c r="O23" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="P23" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.731</v>
+        <v>0.729</v>
       </c>
       <c r="R23" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>40.9</v>
+        <v>41.2</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
@@ -4540,31 +4607,31 @@
         <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA23" t="n">
         <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF23" t="n">
         <v>26</v>
@@ -4579,19 +4646,19 @@
         <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4606,28 +4673,28 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
         <v>23</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AZ23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24" t="n">
         <v>14</v>
       </c>
       <c r="F24" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G24" t="n">
-        <v>0.219</v>
+        <v>0.222</v>
       </c>
       <c r="H24" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="J24" t="n">
-        <v>81.3</v>
+        <v>81</v>
       </c>
       <c r="K24" t="n">
-        <v>0.408</v>
+        <v>0.409</v>
       </c>
       <c r="L24" t="n">
         <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="N24" t="n">
-        <v>0.319</v>
+        <v>0.32</v>
       </c>
       <c r="O24" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P24" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.677</v>
+        <v>0.68</v>
       </c>
       <c r="R24" t="n">
         <v>11.6</v>
       </c>
       <c r="S24" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T24" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="U24" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V24" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="W24" t="n">
         <v>9.800000000000001</v>
@@ -4728,22 +4795,22 @@
         <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>90.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AC24" t="n">
         <v>-10.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,13 +4822,13 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
@@ -4770,13 +4837,13 @@
         <v>13</v>
       </c>
       <c r="AM24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN24" t="n">
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
         <v>10</v>
@@ -4785,16 +4852,16 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
       </c>
       <c r="AT24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,13 +4870,13 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
         <v>25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -4847,43 +4914,43 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F25" t="n">
         <v>32</v>
       </c>
       <c r="G25" t="n">
-        <v>0.515</v>
+        <v>0.508</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J25" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L25" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O25" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P25" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q25" t="n">
         <v>0.774</v>
@@ -4898,7 +4965,7 @@
         <v>43</v>
       </c>
       <c r="U25" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V25" t="n">
         <v>15.2</v>
@@ -4916,16 +4983,16 @@
         <v>22.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB25" t="n">
         <v>104.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4946,28 +5013,28 @@
         <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN25" t="n">
         <v>12</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
         <v>17</v>
@@ -4976,25 +5043,25 @@
         <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV25" t="n">
         <v>25</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F26" t="n">
         <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.677</v>
+        <v>0.672</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J26" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0.444</v>
@@ -5056,16 +5123,16 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O26" t="n">
         <v>16.1</v>
       </c>
       <c r="P26" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="Q26" t="n">
         <v>0.801</v>
@@ -5074,25 +5141,25 @@
         <v>10.8</v>
       </c>
       <c r="S26" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="T26" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="U26" t="n">
         <v>22</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
         <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
         <v>18.6</v>
@@ -5101,31 +5168,31 @@
         <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.5</v>
+        <v>102.4</v>
       </c>
       <c r="AC26" t="n">
         <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
         <v>4</v>
       </c>
       <c r="AG26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI26" t="n">
         <v>10</v>
       </c>
       <c r="AJ26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>25</v>
@@ -5149,13 +5216,13 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" t="n">
         <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>0.349</v>
+        <v>0.339</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
@@ -5229,7 +5296,7 @@
         <v>36.3</v>
       </c>
       <c r="J27" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K27" t="n">
         <v>0.451</v>
@@ -5241,7 +5308,7 @@
         <v>16</v>
       </c>
       <c r="N27" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O27" t="n">
         <v>22.8</v>
@@ -5250,22 +5317,22 @@
         <v>29.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R27" t="n">
         <v>11.1</v>
       </c>
       <c r="S27" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T27" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V27" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
@@ -5274,7 +5341,7 @@
         <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z27" t="n">
         <v>21</v>
@@ -5283,25 +5350,25 @@
         <v>24.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.2</v>
+        <v>-4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5352,16 +5419,16 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>0.629</v>
+        <v>0.635</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,43 +5478,43 @@
         <v>38.2</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O28" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q28" t="n">
         <v>0.772</v>
       </c>
       <c r="R28" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U28" t="n">
         <v>23.9</v>
       </c>
       <c r="V28" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W28" t="n">
         <v>7.8</v>
@@ -5471,16 +5538,16 @@
         <v>4.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
         <v>6</v>
       </c>
       <c r="AG28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5501,46 +5568,46 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
         <v>13</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
         <v>10</v>
       </c>
       <c r="BA28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB28" t="n">
         <v>11</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5665,7 +5732,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI29" t="n">
         <v>9</v>
@@ -5689,19 +5756,19 @@
         <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>3</v>
       </c>
       <c r="AR29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU29" t="n">
         <v>22</v>
@@ -5710,19 +5777,19 @@
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>20</v>
@@ -5871,7 +5938,7 @@
         <v>15</v>
       </c>
       <c r="AP30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ30" t="n">
         <v>25</v>
@@ -5880,10 +5947,10 @@
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>28</v>
@@ -5892,13 +5959,13 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ30" t="n">
         <v>8</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,7 +6096,7 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6053,16 +6120,16 @@
         <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR31" t="n">
         <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>9</v>
@@ -6083,10 +6150,10 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-11-2014-15</t>
+          <t>2015-03-11</t>
         </is>
       </c>
     </row>
